--- a/artfynd/A 62412-2023 artfynd.xlsx
+++ b/artfynd/A 62412-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62412-2023 artfynd.xlsx
+++ b/artfynd/A 62412-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108852107</v>
+        <v>108851222</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mjösebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554707.7896533076</v>
+        <v>554731</v>
       </c>
       <c r="R2" t="n">
-        <v>6331757.471847289</v>
+        <v>6331724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +743,14 @@
           <t>2022-01-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-01-26</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,37 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108851222</v>
+        <v>108851266</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554731.6205811406</v>
+        <v>554730</v>
       </c>
       <c r="R3" t="n">
-        <v>6331724.130526951</v>
+        <v>6331730</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,24 +860,9 @@
           <t>2022-01-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-01-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,15 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108852106</v>
+        <v>100453562</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,42 +915,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mjösebo, Sm</t>
+          <t>Mjösebotrakten, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554718.1584994773</v>
+        <v>554823</v>
       </c>
       <c r="R4" t="n">
-        <v>6331754.894946342</v>
+        <v>6331608</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,22 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-01-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-01-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,46 +990,30 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktor Eriksson</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Eriksson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108851266</v>
+        <v>108852106</v>
       </c>
       <c r="B5" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,34 +1021,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mjösebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554730.453777926</v>
+        <v>554718</v>
       </c>
       <c r="R5" t="n">
-        <v>6331730.086500801</v>
+        <v>6331755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,19 +1083,9 @@
           <t>2022-01-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-01-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,15 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108852102</v>
+        <v>108852107</v>
       </c>
       <c r="B6" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554719.2317899218</v>
+        <v>554708</v>
       </c>
       <c r="R6" t="n">
-        <v>6331755.994875338</v>
+        <v>6331758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,19 +1200,9 @@
           <t>2022-01-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-01-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,6 +1241,123 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>108852102</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mjösebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>554719</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6331756</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Viktor Eriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Viktor Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62412-2023 artfynd.xlsx
+++ b/artfynd/A 62412-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108851222</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108851266</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100453562</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108852106</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108852107</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,8 +1388,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108852102</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>